--- a/data/trans_bre/P32B-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P32B-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; -0,21</t>
+          <t>-2,82; -0,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; -0,97</t>
+          <t>-3,72; -1,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,47</t>
+          <t>-2,43; 0,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,11</t>
+          <t>-0,78; 2,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 244,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,64</t>
+          <t>-1,0; 1,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 0,13</t>
+          <t>-3,0; 0,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,27; -0,56</t>
+          <t>-4,35; -0,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 3,31</t>
+          <t>-2,8; 2,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 589,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 66,59</t>
+          <t>-100,0; 55,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -9,0</t>
+          <t>-100,0; -10,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,05; 225,97</t>
+          <t>-74,99; 187,86</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,09; -0,23</t>
+          <t>-2,13; -0,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; -0,22</t>
+          <t>-4,02; -0,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; -0,25</t>
+          <t>-2,67; -0,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,83</t>
+          <t>-1,84; 2,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 89,37</t>
+          <t>-100,0; 14,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-97,31; 840,89</t>
+          <t>-97,88; 980,39</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 3,83</t>
+          <t>-0,09; 3,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,62; -1,57</t>
+          <t>-5,55; -1,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 1,57</t>
+          <t>-2,15; 1,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,39; -0,15</t>
+          <t>-4,31; -0,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,14; 1357,2</t>
+          <t>-35,55; 1268,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-92,45; -28,2</t>
+          <t>-94,25; -29,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-67,82; 97,99</t>
+          <t>-64,66; 110,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-88,9; 3,96</t>
+          <t>-91,34; -8,05</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,13</t>
+          <t>-0,46; 1,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,25; -1,28</t>
+          <t>-3,14; -1,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; -0,17</t>
+          <t>-1,94; -0,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,53</t>
+          <t>-1,9; 0,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-55,96; 229,68</t>
+          <t>-46,95; 198,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-90,83; -51,14</t>
+          <t>-90,03; -46,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-77,36; -6,63</t>
+          <t>-75,0; -5,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-69,88; 38,15</t>
+          <t>-74,6; 26,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32B-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P32B-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; -0,21</t>
+          <t>-2,43; -0,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,72; -1,04</t>
+          <t>-3,48; -0,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,43</t>
+          <t>-2,5; 0,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,23</t>
+          <t>-0,69; 2,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,78</t>
+          <t>-1,08; 1,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 0,13</t>
+          <t>-3,15; 0,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,35; -0,72</t>
+          <t>-4,68; -0,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 2,94</t>
+          <t>-2,3; 2,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 593,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 55,2</t>
+          <t>-100,0; 60,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -10,11</t>
+          <t>-100,0; -11,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,99; 187,86</t>
+          <t>-73,24; 188,64</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>30,5%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; -0,23</t>
+          <t>-2,26; -0,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; -0,55</t>
+          <t>-4,14; -0,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,67; -0,25</t>
+          <t>-2,52; -0,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,87</t>
+          <t>-2,03; 4,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 14,76</t>
+          <t>-100,0; 15,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-97,88; 980,39</t>
+          <t>-84,7; 581,12</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,05</t>
+          <t>-1,6</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-66,36%</t>
+          <t>-48,16%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 3,83</t>
+          <t>-0,06; 3,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,55; -1,36</t>
+          <t>-5,74; -1,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,79</t>
+          <t>-2,22; 1,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,31; -0,38</t>
+          <t>-3,56; 1,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 1268,31</t>
+          <t>-37,79; 1155,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-94,25; -29,1</t>
+          <t>-94,44; -29,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,66; 110,0</t>
+          <t>-65,75; 116,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-91,34; -8,05</t>
+          <t>-82,39; 92,05</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-32,79%</t>
+          <t>-12,52%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,11</t>
+          <t>-0,49; 1,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,14; -1,22</t>
+          <t>-3,12; -1,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; -0,18</t>
+          <t>-1,99; -0,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,44</t>
+          <t>-1,39; 1,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 198,62</t>
+          <t>-48,24; 199,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-90,03; -46,31</t>
+          <t>-89,95; -46,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-75,0; -5,95</t>
+          <t>-75,36; -1,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-74,6; 26,98</t>
+          <t>-54,2; 69,77</t>
         </is>
       </c>
     </row>
